--- a/artfynd/A 22669-2025 artfynd.xlsx
+++ b/artfynd/A 22669-2025 artfynd.xlsx
@@ -2803,7 +2803,7 @@
         <v>126678770</v>
       </c>
       <c r="B22" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 22669-2025 artfynd.xlsx
+++ b/artfynd/A 22669-2025 artfynd.xlsx
@@ -2803,7 +2803,7 @@
         <v>126678770</v>
       </c>
       <c r="B22" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 22669-2025 artfynd.xlsx
+++ b/artfynd/A 22669-2025 artfynd.xlsx
@@ -2803,7 +2803,7 @@
         <v>126678770</v>
       </c>
       <c r="B22" t="n">
-        <v>80117</v>
+        <v>80114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 22669-2025 artfynd.xlsx
+++ b/artfynd/A 22669-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117140659</v>
+        <v>117140652</v>
       </c>
       <c r="B2" t="n">
-        <v>90459</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605936</v>
+        <v>606141</v>
       </c>
       <c r="R2" t="n">
-        <v>6959299</v>
+        <v>6959168</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117140658</v>
+        <v>117140653</v>
       </c>
       <c r="B3" t="n">
-        <v>74556</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605901</v>
+        <v>606218</v>
       </c>
       <c r="R3" t="n">
-        <v>6959347</v>
+        <v>6959092</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117140634</v>
+        <v>117140651</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606329</v>
+        <v>606144</v>
       </c>
       <c r="R4" t="n">
-        <v>6959262</v>
+        <v>6959183</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117140641</v>
+        <v>117140639</v>
       </c>
       <c r="B5" t="n">
-        <v>90805</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>392</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606276</v>
+        <v>606317</v>
       </c>
       <c r="R5" t="n">
-        <v>6959203</v>
+        <v>6959176</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117140645</v>
+        <v>117140659</v>
       </c>
       <c r="B6" t="n">
-        <v>79525</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605993</v>
+        <v>605936</v>
       </c>
       <c r="R6" t="n">
-        <v>6959340</v>
+        <v>6959299</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117140650</v>
+        <v>117140648</v>
       </c>
       <c r="B7" t="n">
-        <v>90474</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606064</v>
+        <v>605937</v>
       </c>
       <c r="R7" t="n">
-        <v>6959223</v>
+        <v>6959469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117140654</v>
+        <v>117140649</v>
       </c>
       <c r="B8" t="n">
-        <v>90447</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>606157</v>
+        <v>606064</v>
       </c>
       <c r="R8" t="n">
-        <v>6959160</v>
+        <v>6959223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117140648</v>
+        <v>117140650</v>
       </c>
       <c r="B9" t="n">
-        <v>90463</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>605937</v>
+        <v>606064</v>
       </c>
       <c r="R9" t="n">
-        <v>6959469</v>
+        <v>6959223</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117140647</v>
+        <v>117140633</v>
       </c>
       <c r="B10" t="n">
-        <v>82223</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>605887</v>
+        <v>606330</v>
       </c>
       <c r="R10" t="n">
-        <v>6959346</v>
+        <v>6959266</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117140639</v>
+        <v>117140637</v>
       </c>
       <c r="B11" t="n">
-        <v>79398</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>392</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>606317</v>
+        <v>606374</v>
       </c>
       <c r="R11" t="n">
-        <v>6959176</v>
+        <v>6959226</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,15 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117140651</v>
+        <v>117140646</v>
       </c>
       <c r="B12" t="n">
-        <v>74548</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>606144</v>
+        <v>606060</v>
       </c>
       <c r="R12" t="n">
-        <v>6959183</v>
+        <v>6959282</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117140649</v>
+        <v>117140647</v>
       </c>
       <c r="B13" t="n">
-        <v>90463</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>606064</v>
+        <v>605887</v>
       </c>
       <c r="R13" t="n">
-        <v>6959223</v>
+        <v>6959346</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,37 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117140656</v>
+        <v>117140641</v>
       </c>
       <c r="B14" t="n">
-        <v>78444</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>606157</v>
+        <v>606276</v>
       </c>
       <c r="R14" t="n">
-        <v>6959208</v>
+        <v>6959203</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,37 +1988,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117140657</v>
+        <v>117140654</v>
       </c>
       <c r="B15" t="n">
-        <v>78444</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4660</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>606045</v>
+        <v>606157</v>
       </c>
       <c r="R15" t="n">
-        <v>6959326</v>
+        <v>6959160</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,37 +2089,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117140646</v>
+        <v>117140656</v>
       </c>
       <c r="B16" t="n">
-        <v>82223</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>606060</v>
+        <v>606157</v>
       </c>
       <c r="R16" t="n">
-        <v>6959282</v>
+        <v>6959208</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,37 +2190,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117140652</v>
+        <v>117140657</v>
       </c>
       <c r="B17" t="n">
-        <v>90725</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>606141</v>
+        <v>606045</v>
       </c>
       <c r="R17" t="n">
-        <v>6959168</v>
+        <v>6959326</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,37 +2291,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117140653</v>
+        <v>117140636</v>
       </c>
       <c r="B18" t="n">
-        <v>90725</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>6439</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2326,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>606218</v>
+        <v>606374</v>
       </c>
       <c r="R18" t="n">
-        <v>6959092</v>
+        <v>6959226</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,15 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117140661</v>
+        <v>117140638</v>
       </c>
       <c r="B19" t="n">
-        <v>57430</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2493,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2517,10 +2427,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>605972</v>
+        <v>606385</v>
       </c>
       <c r="R19" t="n">
-        <v>6959226</v>
+        <v>6959206</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,15 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117140644</v>
+        <v>117140658</v>
       </c>
       <c r="B20" t="n">
-        <v>79525</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,21 +2504,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2528,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>606015</v>
+        <v>605901</v>
       </c>
       <c r="R20" t="n">
-        <v>6959374</v>
+        <v>6959347</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,15 +2594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117140662</v>
+        <v>117140635</v>
       </c>
       <c r="B21" t="n">
-        <v>79525</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,10 +2629,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>605972</v>
+        <v>606358</v>
       </c>
       <c r="R21" t="n">
-        <v>6959226</v>
+        <v>6959262</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,11 +2665,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-05-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>på gammal grov rönn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2695,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126678770</v>
+        <v>117140644</v>
       </c>
       <c r="B22" t="n">
-        <v>80117</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2831,14 +2726,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Killinghalsmyran, Mpd</t>
+          <t>Honkasosvedjan, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>606363</v>
+        <v>606015</v>
       </c>
       <c r="R22" t="n">
-        <v>6959130</v>
+        <v>6959374</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,12 +2760,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2024-05-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2885,15 +2780,626 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>117140645</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Honkasosvedjan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>605993</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6959340</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>117140662</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Honkasosvedjan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>605972</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6959226</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>på gammal grov rönn</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126678770</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Killinghalsmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>606363</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6959130</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>117140661</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Honkasosvedjan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>605972</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6959226</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>117140634</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Honkasosvedjan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>606329</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6959262</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>117140643</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Honkasosvedjan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>605991</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6959415</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-05-19</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22669-2025 artfynd.xlsx
+++ b/artfynd/A 22669-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140652</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140653</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140651</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140639</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140659</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140648</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140649</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140650</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140633</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140637</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140646</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140647</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140641</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140654</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140656</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140657</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140636</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140638</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140658</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140635</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140644</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,6 +3004,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140645</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3000,6 +3115,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140662</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3097,6 +3217,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126678770</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3198,6 +3323,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140661</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3299,6 +3429,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140634</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3400,8 +3535,42 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117140643</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>